--- a/results/class_sensitivity/recurrence_vs_hsp90_class_sensitivity.xlsx
+++ b/results/class_sensitivity/recurrence_vs_hsp90_class_sensitivity.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3482857614109044</v>
+        <v>0.3219302256926899</v>
       </c>
     </row>
     <row r="4">
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02209412254134318</v>
+        <v>0.03527059433645797</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01413530961404498</v>
+        <v>-0.02216379480258373</v>
       </c>
     </row>
     <row r="8">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6251397847767993</v>
+        <v>0.5992997586054034</v>
       </c>
     </row>
     <row r="9">
@@ -550,7 +550,7 @@
         <v>-0.1786272139903385</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.3205128205128205</v>
       </c>
     </row>
     <row r="3">
@@ -576,7 +576,7 @@
         <v>-0.2094323762561981</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6499999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -628,7 +628,7 @@
         <v>-0.2183080445642374</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6793381037567083</v>
+        <v>0.6279069767441861</v>
       </c>
     </row>
     <row r="9">
@@ -641,7 +641,7 @@
         <v>-0.1662653967408163</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6</v>
+        <v>0.5391472868217054</v>
       </c>
     </row>
     <row r="10">
@@ -693,7 +693,7 @@
         <v>-0.2235656201793519</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7897435897435897</v>
+        <v>0.7333333333333333</v>
       </c>
     </row>
     <row r="14">
@@ -706,7 +706,7 @@
         <v>-0.2064610311547386</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7441860465116279</v>
+        <v>0.772093023255814</v>
       </c>
     </row>
     <row r="15">
@@ -719,7 +719,7 @@
         <v>-0.2082082076743421</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2583333333333333</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="16">
@@ -758,7 +758,7 @@
         <v>-0.1414054398988475</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6976744186046512</v>
+        <v>0.7626303127506014</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         <v>-0.1783653544666676</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.7404761904761905</v>
       </c>
     </row>
     <row r="20">
@@ -784,7 +784,7 @@
         <v>-0.2272999068630794</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.2562015503875969</v>
       </c>
     </row>
     <row r="21">
@@ -810,7 +810,7 @@
         <v>-0.2357862821744499</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1162790697674419</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="23">
@@ -823,7 +823,7 @@
         <v>-0.1928960493937777</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.296551724137931</v>
       </c>
     </row>
     <row r="24">
@@ -836,7 +836,7 @@
         <v>-0.1891070006869582</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.6252236135957066</v>
       </c>
     </row>
     <row r="25">
@@ -849,7 +849,7 @@
         <v>-0.1679123265606992</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7690476190476191</v>
+        <v>0.6511627906976745</v>
       </c>
     </row>
     <row r="26">
@@ -862,7 +862,7 @@
         <v>-0.2002121226750436</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4775193798449612</v>
       </c>
     </row>
     <row r="27">
@@ -888,7 +888,7 @@
         <v>-0.1820048265378515</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1785714285714286</v>
+        <v>0.1726190476190476</v>
       </c>
     </row>
     <row r="29">
@@ -914,7 +914,7 @@
         <v>-0.1998464016445489</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3928571428571428</v>
+        <v>0.3964285714285715</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +927,7 @@
         <v>-0.205184187788136</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8023255813953489</v>
+        <v>0.7666666666666667</v>
       </c>
     </row>
     <row r="32">
@@ -940,7 +940,7 @@
         <v>-0.184285453771279</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.7998338870431894</v>
       </c>
     </row>
     <row r="33">
@@ -953,7 +953,7 @@
         <v>-0.194595351118395</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2452934662236988</v>
+        <v>0.2884615384615384</v>
       </c>
     </row>
     <row r="34">
@@ -979,7 +979,7 @@
         <v>-0.226134911817538</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8418604651162791</v>
+        <v>0.9615384615384616</v>
       </c>
     </row>
     <row r="36">
@@ -992,7 +992,7 @@
         <v>-0.222738672149269</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.2870879120879121</v>
       </c>
     </row>
     <row r="37">
@@ -1031,7 +1031,7 @@
         <v>-0.2418526659406501</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.2012820512820513</v>
       </c>
     </row>
     <row r="40">
@@ -1057,7 +1057,7 @@
         <v>-0.2392060740558485</v>
       </c>
       <c r="C41" t="n">
-        <v>0.7</v>
+        <v>0.643103448275862</v>
       </c>
     </row>
     <row r="42">
@@ -1070,7 +1070,7 @@
         <v>-0.2246998597349494</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5952380952380952</v>
+        <v>0.692970822281167</v>
       </c>
     </row>
     <row r="43">
@@ -1096,7 +1096,7 @@
         <v>-0.1611385731101388</v>
       </c>
       <c r="C44" t="n">
-        <v>0.8</v>
+        <v>0.8069767441860465</v>
       </c>
     </row>
   </sheetData>

--- a/results/class_sensitivity/recurrence_vs_hsp90_class_sensitivity.xlsx
+++ b/results/class_sensitivity/recurrence_vs_hsp90_class_sensitivity.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3219302256926899</v>
+        <v>0.3541005930736624</v>
       </c>
     </row>
     <row r="4">
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03527059433645797</v>
+        <v>0.01982647096370697</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.02216379480258373</v>
+        <v>0.02057184723695619</v>
       </c>
     </row>
     <row r="8">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5992997586054034</v>
+        <v>0.6363704291757203</v>
       </c>
     </row>
     <row r="9">
@@ -550,7 +550,7 @@
         <v>-0.1786272139903385</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3205128205128205</v>
+        <v>0.2701252236135957</v>
       </c>
     </row>
     <row r="3">
@@ -576,7 +576,7 @@
         <v>-0.2094323762561981</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6499999999999999</v>
+        <v>0.6821705426356589</v>
       </c>
     </row>
     <row r="5">
@@ -628,7 +628,7 @@
         <v>-0.2183080445642374</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6279069767441861</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="9">
@@ -641,7 +641,7 @@
         <v>-0.1662653967408163</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5391472868217054</v>
+        <v>0.5833333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -719,7 +719,7 @@
         <v>-0.2082082076743421</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3</v>
+        <v>0.2666666666666667</v>
       </c>
     </row>
     <row r="16">
@@ -758,7 +758,7 @@
         <v>-0.1414054398988475</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7626303127506014</v>
+        <v>0.7655038759689923</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         <v>-0.1783653544666676</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7404761904761905</v>
+        <v>0.7670542635658915</v>
       </c>
     </row>
     <row r="20">
@@ -784,7 +784,7 @@
         <v>-0.2272999068630794</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2562015503875969</v>
+        <v>0.2238095238095238</v>
       </c>
     </row>
     <row r="21">
@@ -797,7 +797,7 @@
         <v>-0.2027319592747009</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4418604651162791</v>
+        <v>0.5116279069767442</v>
       </c>
     </row>
     <row r="22">
@@ -810,7 +810,7 @@
         <v>-0.2357862821744499</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2</v>
+        <v>0.1581395348837209</v>
       </c>
     </row>
     <row r="23">
@@ -823,7 +823,7 @@
         <v>-0.1928960493937777</v>
       </c>
       <c r="C23" t="n">
-        <v>0.296551724137931</v>
+        <v>0.3761904761904762</v>
       </c>
     </row>
     <row r="24">
@@ -849,7 +849,7 @@
         <v>-0.1679123265606992</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6511627906976745</v>
+        <v>0.7380952380952381</v>
       </c>
     </row>
     <row r="26">
@@ -862,7 +862,7 @@
         <v>-0.2002121226750436</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4775193798449612</v>
+        <v>0.4666666666666667</v>
       </c>
     </row>
     <row r="27">
@@ -927,7 +927,7 @@
         <v>-0.205184187788136</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.7674418604651163</v>
       </c>
     </row>
     <row r="32">
@@ -940,7 +940,7 @@
         <v>-0.184285453771279</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7998338870431894</v>
+        <v>0.7761904761904762</v>
       </c>
     </row>
     <row r="33">
@@ -953,7 +953,7 @@
         <v>-0.194595351118395</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2884615384615384</v>
+        <v>0.2666666666666667</v>
       </c>
     </row>
     <row r="34">
@@ -966,7 +966,7 @@
         <v>-0.2238031966272546</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2093023255813954</v>
+        <v>0.2008050089445438</v>
       </c>
     </row>
     <row r="35">
@@ -979,7 +979,7 @@
         <v>-0.226134911817538</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9615384615384616</v>
+        <v>0.8837209302325582</v>
       </c>
     </row>
     <row r="36">
@@ -992,7 +992,7 @@
         <v>-0.222738672149269</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2870879120879121</v>
+        <v>0.2380952380952381</v>
       </c>
     </row>
     <row r="37">
@@ -1031,7 +1031,7 @@
         <v>-0.2418526659406501</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2012820512820513</v>
+        <v>0.1333333333333333</v>
       </c>
     </row>
     <row r="40">
@@ -1057,7 +1057,7 @@
         <v>-0.2392060740558485</v>
       </c>
       <c r="C41" t="n">
-        <v>0.643103448275862</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="42">
@@ -1070,7 +1070,7 @@
         <v>-0.2246998597349494</v>
       </c>
       <c r="C42" t="n">
-        <v>0.692970822281167</v>
+        <v>0.680952380952381</v>
       </c>
     </row>
     <row r="43">
